--- a/AAII_Financials/Quarterly/MRK_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MRK_QTR_FIN.xlsx
@@ -656,531 +656,543 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="21" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="22" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="43" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42916</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42825</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>16607000</v>
+      </c>
+      <c r="E8" s="3">
         <v>16286000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>16400000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>17276000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>15806000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>15529000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>15624000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>16657000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>16112000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>15775000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>14630000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>15962000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>15035000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>14487000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>13830000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>14959000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>14593000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>15901000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>13521000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>13154000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>11402000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>10627000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>10948000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>10929000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>9353000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>12057000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>11868000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>12397000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>11760000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>10816000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>10998000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>10794000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>10465000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>10037000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>10433000</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>10325000</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>9930000</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>9434000</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>10115000</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>10536000</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>4128000</v>
+      </c>
+      <c r="E9" s="3">
         <v>3875000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>4295000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>3745000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>3392000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>3383000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>3707000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>3888000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>3679000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>3424000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>3795000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>4231000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>3992000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>3897000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>3843000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>3880000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>4149000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>5334000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>3827000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>3402000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>3029000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>2984000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>4725000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>3260000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>3021000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>3244000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>2874000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>3928000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>3336000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>3018000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>3276000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>3197000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>3414000</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>3178000</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>3378000</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>3249000</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>3000000</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>2876000</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>3300000</v>
       </c>
-      <c r="AP9" s="3">
+      <c r="AQ9" s="3">
         <v>3373000</v>
       </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>12479000</v>
+      </c>
+      <c r="E10" s="3">
         <v>12411000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>12105000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>13531000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>12414000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>12146000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>11917000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>12769000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>12433000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>12351000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>10835000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>11731000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>11043000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>10590000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>9987000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>11079000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>10444000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>10567000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>9694000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>9752000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>8373000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>7643000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>6223000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>7669000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>6332000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>8813000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>8994000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>8469000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>8424000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>7798000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>7722000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>7597000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>7051000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>6859000</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>7055000</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>7076000</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>6930000</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>6558000</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>6815000</v>
       </c>
-      <c r="AP10" s="3">
+      <c r="AQ10" s="3">
         <v>7163000</v>
       </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1223,130 +1235,134 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>9742000</v>
+      </c>
+      <c r="E12" s="3">
         <v>3558000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>3997000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>4001000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>3995000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>3521000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>1129000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>5862000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>3500000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>3334000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>8848000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>3307000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>2622000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>3084000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>2962000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>3511000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>2776000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>2569000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>3061000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>2437000</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>2611000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>2404000</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>2650000</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>3330000</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>2054000</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>2192000</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>2376000</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>3203000</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>2186000</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>1931000</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>2061000</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>2072000</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>1927000</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>1794000</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AL12" s="3">
         <v>2051000</v>
       </c>
-      <c r="AL12" s="3">
+      <c r="AM12" s="3">
         <v>4136000</v>
       </c>
-      <c r="AM12" s="3">
+      <c r="AN12" s="3">
         <v>1740000</v>
       </c>
-      <c r="AN12" s="3">
+      <c r="AO12" s="3">
         <v>1796000</v>
       </c>
-      <c r="AO12" s="3">
+      <c r="AP12" s="3">
         <v>1265000</v>
       </c>
-      <c r="AP12" s="3">
+      <c r="AQ12" s="3">
         <v>1645000</v>
       </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1467,175 +1483,181 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>175000</v>
+      </c>
+      <c r="E14" s="3">
         <v>9381000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>1555000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>17000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>679000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>115000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>3628000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>310000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>121000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>759000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>1079500</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>232000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>11109000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>1411500</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>900000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>1062000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>258000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>127000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>238000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>168000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>1869000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>522000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>3762000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>185000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>149000</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>168000</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>1162000</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>295000</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>159000</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>187000</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>336000</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>589000</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>576000</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>1504000</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>567000</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AM14" s="3">
         <v>436000</v>
       </c>
-      <c r="AM14" s="3">
+      <c r="AN14" s="3">
         <v>257000</v>
       </c>
-      <c r="AN14" s="3">
+      <c r="AO14" s="3">
         <v>291000</v>
       </c>
-      <c r="AO14" s="3">
+      <c r="AP14" s="3">
         <v>4335000</v>
       </c>
-      <c r="AP14" s="3">
+      <c r="AQ14" s="3">
         <v>215000</v>
       </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>1468000</v>
+      </c>
+      <c r="E15" s="3">
         <v>1404000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>1418000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>1098000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>1064000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>1058000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>1114000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>1146000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>1066000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>919000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>903000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>978000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>881000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>970000</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
-      </c>
       <c r="R15" s="3">
         <v>0</v>
       </c>
@@ -1711,8 +1733,11 @@
       <c r="AP15" s="3">
         <v>0</v>
       </c>
+      <c r="AQ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1752,252 +1777,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>16647000</v>
+      </c>
+      <c r="E17" s="3">
         <v>9999000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>11025000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>10227000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>9883000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>9308000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>7527000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>12293000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>9728000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>9076000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>15284000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>9879000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>9153000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>9344000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>10392000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>10947000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>9668000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>10332000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>9946000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>8338000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>9788000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>8095000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>13746000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>8535000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>6999000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>8148000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>9300000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>10015000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>8361000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>7561000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>8284000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>8301000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>8427000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>8983000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>8572000</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>10211000</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>7433000</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>7373000</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>11464000</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>7625000</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>-40000</v>
+      </c>
+      <c r="E18" s="3">
         <v>6287000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>5375000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>7049000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>5923000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>6221000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>8097000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>4364000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>6384000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>6699000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-654000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>6083000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>5882000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>5143000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>3438000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>4012000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>4925000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>5569000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>3575000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>4816000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>1614000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>2532000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-2798000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>2394000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>2354000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>3909000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>2568000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>2382000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>3399000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>3255000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>2714000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>2493000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>2038000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>1054000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>1861000</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>114000</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>2497000</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>2061000</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>-1349000</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>2911000</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -2040,618 +2072,634 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>-22000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-4000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>58000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>56000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>9000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-1000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>117000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-239000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>16000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>40000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>72500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-13000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-60000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-48500</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>310000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-185000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-198000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-465000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>543000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>646000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>305000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>654000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>460000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>515000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>596000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>141000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>442000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>196000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>93000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>21000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>93000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>362000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>242000</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>476000</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>208000</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>275000</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>135000</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>124000</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>173000</v>
       </c>
-      <c r="AP20" s="3">
+      <c r="AQ20" s="3">
         <v>146000</v>
       </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>1450000</v>
+      </c>
+      <c r="E21" s="3">
         <v>7695000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>6735000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>8091000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>6978000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>7280000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>9094000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>5749000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>7434000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>7578000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>176500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>7074000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>6823000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>6161500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>4640000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>4786000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>5665000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>6224000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>4953000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>6221000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>2609000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>4116000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-1455000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>3716000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>3925000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>4871000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>3946000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>3423000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>4465000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>4174000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>3805000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>4013000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>3506000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>2667000</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>3197000</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>1543000</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>3794000</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>3378000</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>-21000</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>4232000</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>525000</v>
+      </c>
+      <c r="E22" s="3">
         <v>479000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>411000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>327000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>305000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>313000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>328000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>330000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>310000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>303000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>310000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>317000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>277000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>242000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>235000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>244000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>240000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>243000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>209000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>196000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>202000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>199000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>207000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>203000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>209000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>212000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>219000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>231000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>233000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>209000</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>203000</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>190000</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>194000</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>185000</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>190000</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>189000</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AN22" s="3">
         <v>193000</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AO22" s="3">
         <v>182000</v>
       </c>
-      <c r="AO22" s="3">
+      <c r="AP22" s="3">
         <v>180000</v>
       </c>
-      <c r="AP22" s="3">
+      <c r="AQ22" s="3">
         <v>170000</v>
       </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>-683000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-3534000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>3420000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>6745000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>4999000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>5903000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>4170000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>4090000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>6006000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>5670000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-2046000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>5620000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-5335000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>3650000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>3513000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>3583000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>4487000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>4861000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>3909000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>5266000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>1717000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>2987000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-2545000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>2706000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>2741000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>3838000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>2791000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>2347000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>3259000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>3067000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>2604000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>2665000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>2086000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>1345000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>1879000</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>200000</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>2439000</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>2003000</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>-1356000</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>2887000</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>654000</v>
+      </c>
+      <c r="E24" s="3">
         <v>709000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>458000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>958000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>571000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>818000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>426000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>929000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>545000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>903000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-820000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>870000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>637000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>825000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>495000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>330000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>538000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>554000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>85000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>695000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>503000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>238000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>69000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>380000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>396000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>619000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>378000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>440000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>615000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>138000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>537000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>707000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>370000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>604000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>317000</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>251000</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>488000</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>447000</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>-769000</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>699000</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -2772,252 +2820,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>-1337000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-4243000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>2962000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>5787000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>4428000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>5085000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>3744000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>3161000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>5461000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>4767000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-1226000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>4750000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-5972000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>2825000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>3018000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>3253000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>3949000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>4307000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>3824000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>4571000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>1214000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>2749000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-2614000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>2326000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>2345000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>3219000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>2413000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>1907000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>2644000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>2929000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>2067000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>1958000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>1716000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>741000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>1562000</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>-51000</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>1951000</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>1556000</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>-587000</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>2188000</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>-1335000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-4240000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>2963000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>5785000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>4427000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>5079000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>3743000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>3157000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>5455000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>4762000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-1226000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>4745000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-5975000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>2821000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>3017000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>3248000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>3944000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>4310000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>3820000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>4567000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>1213000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>2738000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-2617000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>2324000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>2341000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>3219000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>2406000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>1901000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>2670000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>2982000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>2116000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>1950000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>1707000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>736000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>1554000</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>-56000</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>1946000</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>1551000</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>-595000</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>2184000</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -3138,8 +3195,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -3195,46 +3255,46 @@
         <v>0</v>
       </c>
       <c r="U29" s="3">
+        <v>0</v>
+      </c>
+      <c r="V29" s="3">
         <v>-62000</v>
       </c>
-      <c r="V29" s="3">
-        <v>0</v>
-      </c>
       <c r="W29" s="3">
+        <v>0</v>
+      </c>
+      <c r="X29" s="3">
         <v>332000</v>
       </c>
-      <c r="X29" s="3">
+      <c r="Y29" s="3">
         <v>434000</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Z29" s="3">
         <v>523000</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="AA29" s="3">
         <v>617000</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AB29" s="3">
         <v>661000</v>
       </c>
-      <c r="AB29" s="3">
-        <v>0</v>
-      </c>
       <c r="AC29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD29" s="3">
         <v>-50000</v>
       </c>
-      <c r="AD29" s="3">
-        <v>0</v>
-      </c>
       <c r="AE29" s="3">
         <v>0</v>
       </c>
       <c r="AF29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG29" s="3">
         <v>-67000</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AH29" s="3">
         <v>-289000</v>
-      </c>
-      <c r="AH29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="AI29" s="3" t="s">
         <v>24</v>
@@ -3242,11 +3302,11 @@
       <c r="AJ29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AK29" s="3">
+      <c r="AK29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="AL29" s="3">
         <v>-2600000</v>
-      </c>
-      <c r="AL29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="AM29" s="3" t="s">
         <v>24</v>
@@ -3260,8 +3320,11 @@
       <c r="AP29" s="3" t="s">
         <v>24</v>
       </c>
+      <c r="AQ29" s="3" t="s">
+        <v>24</v>
+      </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3382,8 +3445,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3504,252 +3570,261 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>22000</v>
+      </c>
+      <c r="E32" s="3">
         <v>4000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-58000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-56000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-9000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>1000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-117000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>239000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-16000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-40000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-72500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>13000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>60000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>48500</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-310000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>185000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>198000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>465000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-543000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-646000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-305000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-654000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-460000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-515000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-596000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-141000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-442000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-196000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-93000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-21000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-93000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-362000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-242000</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-476000</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-208000</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-275000</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>-135000</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>-124000</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>-173000</v>
       </c>
-      <c r="AP32" s="3">
+      <c r="AQ32" s="3">
         <v>-146000</v>
       </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-1335000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-4240000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>2963000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>5785000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>4427000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>5079000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>3743000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>3157000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>5455000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>4762000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-1226000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>4745000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-5975000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>2821000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>3017000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>3248000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>3944000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>4310000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>3758000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>4567000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>1545000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>3172000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-2094000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>2941000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>3002000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>3219000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>2356000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>1901000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>2670000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>2915000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>1827000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>1950000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>1707000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>736000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>-1046000</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>-56000</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>1946000</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>1551000</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>-595000</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>2184000</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3870,257 +3945,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-1335000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-4240000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>2963000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>5785000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>4427000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>5079000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>3743000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>3157000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>5455000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>4762000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-1226000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>4745000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-5975000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>2821000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>3017000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>3248000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>3944000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>4310000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>3758000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>4567000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>1545000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>3172000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-2094000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>2941000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>3002000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>3219000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>2356000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>1901000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>2670000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>2915000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>1827000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>1950000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>1707000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>736000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>-1046000</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>-56000</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>1946000</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>1551000</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>-595000</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>2184000</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42916</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42825</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4163,8 +4247,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4207,186 +4292,190 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>6849000</v>
+      </c>
+      <c r="E41" s="3">
         <v>5327000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>14565000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>18169000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>8007000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>8629000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>13242000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>14593000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>11304000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>5579000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>6841000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>8605000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>5660000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>9707000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>12694000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>11145000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>9675000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>8556000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>8096000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>10016000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>8575000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>6981000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>8062000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>7356000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>11103000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>7425000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>9676000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>7869000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>6659000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>8076000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>7965000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>7826000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>5310000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>4483000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>6092000</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>7901000</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>7786000</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>11708000</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>6515000</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>7907000</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>292000</v>
+      </c>
+      <c r="E42" s="3">
         <v>375000</v>
       </c>
-      <c r="E42" s="3">
-        <v>0</v>
-      </c>
       <c r="F42" s="3">
+        <v>0</v>
+      </c>
+      <c r="G42" s="3">
         <v>45000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>615000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>599000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>447000</v>
       </c>
-      <c r="J42" s="3">
-        <v>0</v>
-      </c>
       <c r="K42" s="3">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3">
         <v>50000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>40000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>252000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>168000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>718000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>680000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>498000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>103000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>453000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>372000</v>
-      </c>
-      <c r="U42" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="V42" s="3" t="s">
         <v>24</v>
@@ -4397,8 +4486,8 @@
       <c r="X42" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="Y42" s="3">
-        <v>0</v>
+      <c r="Y42" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="Z42" s="3">
         <v>0</v>
@@ -4407,906 +4496,930 @@
         <v>0</v>
       </c>
       <c r="AB42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC42" s="3">
         <v>7000</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>774000</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>149000</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>446000</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>722000</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>899000</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>2459000</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>2284000</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>2863000</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>2406000</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AM42" s="3">
         <v>3294000</v>
       </c>
-      <c r="AM42" s="3">
+      <c r="AN42" s="3">
         <v>4181000</v>
       </c>
-      <c r="AN42" s="3">
+      <c r="AO42" s="3">
         <v>3541000</v>
       </c>
-      <c r="AO42" s="3">
+      <c r="AP42" s="3">
         <v>7826000</v>
       </c>
-      <c r="AP42" s="3">
+      <c r="AQ42" s="3">
         <v>5160000</v>
       </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>13428000</v>
+      </c>
+      <c r="E43" s="3">
         <v>13051000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>12706000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>12999000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>12716000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>11584000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>11127000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>12544000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>12971000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>12572000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>11072000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>11674000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>12338000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>11577000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>10110000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>10118000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>10334000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>10473000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>9230000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>8571000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>7843000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>8235000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>7851000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>8422000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>7577000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>8182000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>6778000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>8442000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>7964000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>7608000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>7071000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>7374000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>7287000</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>7245000</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>6873000</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>7671000</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>7439000</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>7066000</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>7018000</v>
       </c>
-      <c r="AP43" s="3">
+      <c r="AQ43" s="3">
         <v>7364000</v>
       </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>6207000</v>
+      </c>
+      <c r="E44" s="3">
         <v>6479000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>6658000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>6444000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>6601000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>6196000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>6109000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>6244000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>6469000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>6510000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>6358000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>6131000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>5930000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>5863000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>5911000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>5614000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>5535000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>5774000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>5953000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>5603000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>5499000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>6402000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>6310000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>6128000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>6056000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>5846000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>5978000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>5855000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>5847000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>5712000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>5440000</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>5416000</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>5178000</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>5382000</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>5096000</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>5263000</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>5407000</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>5146000</v>
       </c>
-      <c r="AO44" s="3">
+      <c r="AP44" s="3">
         <v>4866000</v>
       </c>
-      <c r="AP44" s="3">
+      <c r="AQ44" s="3">
         <v>5244000</v>
       </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>9861000</v>
+      </c>
+      <c r="E45" s="3">
         <v>9712000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>9462000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>9809000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>9060000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>8392000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>7781000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>6885000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>7342000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>6652000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>7577000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>5312000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>5279000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>5496000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>6509000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>6581000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>6119000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>6009000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>6987000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>6868000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>6748000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>5291000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>5541000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>4671000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>4607000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>4714000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>4277000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>3827000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>3382000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>3233000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>4500000</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>3761000</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>4005000</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>4112000</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>4299000</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>3790000</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>3354000</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>4069000</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>4389000</v>
       </c>
-      <c r="AP45" s="3">
+      <c r="AQ45" s="3">
         <v>3765000</v>
       </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>36679000</v>
+      </c>
+      <c r="E46" s="3">
         <v>35015000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>43516000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>47557000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>37065000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>35503000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>38782000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>40361000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>38205000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>31445000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>32168000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>31954000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>29977000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>33402000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>35722000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>33561000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>32116000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>31184000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>30266000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>31058000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>28665000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>26909000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>27764000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>26577000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>29343000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>26174000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>27483000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>26142000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>24298000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>25351000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>25875000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>26836000</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>24064000</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>24085000</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>24766000</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>27919000</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>28167000</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>31530000</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>30614000</v>
       </c>
-      <c r="AP46" s="3">
+      <c r="AQ46" s="3">
         <v>29440000</v>
       </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>2352000</v>
+      </c>
+      <c r="E47" s="3">
         <v>2281000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>2082000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>2257000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>1941000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>1793000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>1610000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>1850000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1601000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1554000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>1558000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>2636000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>2785000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>2958000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>2445000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>2344000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>1714000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>2159000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>966000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>1013000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>1105000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>1195000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>1371000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>1880000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>1738000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>1005000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>1469000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>2111000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>3779000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>5621000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>6233000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>7606000</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>10033000</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>11033000</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>12892000</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>12206000</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>12138000</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>11896000</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AP47" s="3">
         <v>12131000</v>
       </c>
-      <c r="AP47" s="3">
+      <c r="AQ47" s="3">
         <v>11657000</v>
       </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>25737000</v>
+      </c>
+      <c r="E48" s="3">
         <v>25433000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>26823000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>25639000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>25236000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>24793000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>25149000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>23446000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>23221000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>23045000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>24488000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>22526000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>22231000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>21758000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>21422000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>20424000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>20059000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>19747000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>19279000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>18565000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>18064000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>18295000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>17986000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>16919000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>15789000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>15269000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>16126000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>15372000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>14925000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>13506000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>13291000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>12755000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>12626000</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>12561000</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>12439000</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>12189000</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>12094000</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>12042000</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>12026000</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>12029000</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>46560000</v>
+      </c>
+      <c r="E49" s="3">
         <v>47326000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>48260000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>36900000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>36784000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>37442000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>38038000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>38707000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>38145000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>38753000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>39208000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>40382000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>40860000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>41066000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>41473000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>42528000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>43710000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>44280000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>44197000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>32246000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>32495000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>34613000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>34842000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>36925000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>36633000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>35863000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>33621000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>31787000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>32871000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>29169000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>29684000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>30433000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>31172000</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>31804000</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>32467000</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>33478000</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>34477000</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>35221000</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>35467000</v>
       </c>
-      <c r="AP49" s="3">
+      <c r="AQ49" s="3">
         <v>38766000</v>
       </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5427,8 +5540,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5549,130 +5665,136 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>18349000</v>
+      </c>
+      <c r="E52" s="3">
         <v>18505000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>13455000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>17193000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>16497000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>15591000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>9926000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>13168000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>11458000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>11052000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>7285000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>9229000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>8616000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>8612000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>8098000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>8224000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>9496000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>9298000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>10986000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>10612000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>10359000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>9835000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>9625000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>7499000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>7112000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>6602000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>5698000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>7919000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>8092000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>8707000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>7554000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>7500000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>7145000</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>6558000</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>5308000</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>5884000</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>5928000</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>5872000</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>5139000</v>
       </c>
-      <c r="AP52" s="3">
+      <c r="AQ52" s="3">
         <v>6443000</v>
       </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5793,130 +5915,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>129802000</v>
+      </c>
+      <c r="E54" s="3">
         <v>128685000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>136866000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>129546000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>117523000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>115122000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>117106000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>117532000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>112630000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>105849000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>106675000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>106727000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>104469000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>107796000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>109160000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>107081000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>107095000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>106668000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>105694000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>93494000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>90688000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>90847000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>91588000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>89800000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>90615000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>84913000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>84397000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>83331000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>83965000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>82354000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>82637000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>85130000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>85040000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>86041000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>87872000</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>91676000</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>92804000</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>96561000</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>95377000</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>98335000</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5959,8 +6087,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -6003,740 +6132,759 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3919000</v>
+      </c>
+      <c r="E57" s="3">
         <v>3962000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>4515000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>4306000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>4023000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>3962000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>4999000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>5468000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>5215000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>5507000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>4434000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>4218000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>3905000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>4293000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>4264000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>3371000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>3482000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>3715000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>4609000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>3366000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>3897000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>4034000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>4594000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>3744000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>3448000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>3572000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>3738000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>3198000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>3142000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>3018000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>3318000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>3091000</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>3024000</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>3162000</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>3102000</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>2620000</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>2934000</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>2484000</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>2807000</v>
       </c>
-      <c r="AP57" s="3">
+      <c r="AQ57" s="3">
         <v>2481000</v>
       </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2825000</v>
+      </c>
+      <c r="E58" s="3">
         <v>2444000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>2883000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1405000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1434000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1360000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>2931000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>3149000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>3071000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>3077000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1657000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>887000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>2839000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>2672000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>1946000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>1936000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>2979000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>1208000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>2412000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>3534000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>2488000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>7251000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>6431000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>2420000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>4718000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>6361000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>3610000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>3411000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>3816000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>3175000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>5308000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>3656000</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>3379000</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>2055000</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>3057000</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>5157000</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>3181000</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>5037000</v>
       </c>
-      <c r="AO58" s="3">
+      <c r="AP58" s="3">
         <v>568000</v>
       </c>
-      <c r="AP58" s="3">
+      <c r="AQ58" s="3">
         <v>1487000</v>
       </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>6754000</v>
+      </c>
+      <c r="E59" s="3">
         <v>6406000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>7189000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>7383000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>7051000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>7548000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>6507000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>6609000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>5020000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>4628000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>5473000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>4168000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>3711000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>4072000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>18029000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>17691000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>16707000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>17393000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>16851000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>16828000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>15521000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>15076000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>16302000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>14241000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>14012000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>13550000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>14872000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>14075000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>13127000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>12350000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>13580000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>11839000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>11725000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>11743000</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>12455000</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>11690000</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>12643000</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>12302000</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>13829000</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>11587000</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>27731000</v>
+      </c>
+      <c r="E60" s="3">
         <v>26945000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>28327000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>28628000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>26037000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>25174000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>28420000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>29586000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>26060000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>25099000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>25694000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>23094000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>23394000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>23131000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>24239000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>22998000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>23168000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>22316000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>23872000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>23728000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>21906000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>26361000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>27327000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>20405000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>22178000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>23483000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>22220000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>20684000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>20085000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>18543000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>22206000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>18586000</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>18128000</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>16960000</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>18614000</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>19467000</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>18758000</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>19823000</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>17204000</v>
       </c>
-      <c r="AP60" s="3">
+      <c r="AQ60" s="3">
         <v>15555000</v>
       </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>51086000</v>
+      </c>
+      <c r="E61" s="3">
         <v>46673000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>47651000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>39969000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>33968000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>33484000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>35339000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>34982000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>34717000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>31142000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>34611000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>33980000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>34072000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>28075000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>28745000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>28482000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>28684000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>30586000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>30690000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>22907000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>24033000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>24002000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>25360000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>26321000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>26156000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>21637000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>22736000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>22677000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>22771000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>22721000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>19806000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>19936000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>19959000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>21501000</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>21353000</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>21838000</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>21706000</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>23437000</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>24274000</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>23656000</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>7568000</v>
+      </c>
+      <c r="E62" s="3">
         <v>7642000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>5948000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>7661000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>7031000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>6655000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>4649000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>7540000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>7329000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>8262000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>6633000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>7335000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>7265000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>8243000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>10118000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>11077000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>11925000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>12813000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>12875000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>10996000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>11361000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>13445000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>13497000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>13804000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>14537000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>13493000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>13440000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>13045000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>13372000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>13420000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>13743000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>13952000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>14187000</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>13679000</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>13336000</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>11872000</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>12628000</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>13213000</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>13591000</v>
       </c>
-      <c r="AP62" s="3">
+      <c r="AQ62" s="3">
         <v>15167000</v>
       </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6857,8 +7005,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -6979,8 +7130,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7101,130 +7255,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>87818000</v>
+      </c>
+      <c r="E66" s="3">
         <v>82754000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>84204000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>77639000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>68463000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>66722000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>70734000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>72972000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>68982000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>65425000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>69040000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>65427000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>65727000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>60891000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>63169000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>62623000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>63852000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>65785000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>67510000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>57700000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>57394000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>63902000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>66271000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>60614000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>62973000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>58708000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>58490000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>56493000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>56330000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>54815000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>55936000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>52708000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>52511000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>52373000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>53536000</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>53428000</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>53341000</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>56724000</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>55289000</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>54591000</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7267,8 +7427,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7389,8 +7550,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7511,8 +7675,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7633,8 +7800,11 @@
       <c r="AP70" s="3">
         <v>0</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7755,130 +7925,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>63269000</v>
+      </c>
+      <c r="E72" s="3">
         <v>66721000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>73075000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>72231000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>68477000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>66097000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>63069000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>61384000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>60187000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>56697000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>53895000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>57082000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>54198000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>62039000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>61081000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>59928000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>58437000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>56252000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>53696000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>51691000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>48777000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>48888000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>47362000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>51107000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>49724000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>48272000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>46602000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>45804000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>45295000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>44065000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>42579000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>42189000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>41523000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>41107000</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>41350000</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>43701000</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>45046000</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>44387000</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>44133000</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>46028000</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7999,8 +8175,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8121,8 +8300,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8243,130 +8425,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>41933000</v>
+      </c>
+      <c r="E76" s="3">
         <v>45878000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>52606000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>51850000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>48993000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>48335000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>46313000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>44502000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>43582000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>40364000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>37581000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>41246000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>38693000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>46834000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>45991000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>44458000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>43243000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>40883000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>38184000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>35794000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>33294000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>26945000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>25317000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>29186000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>27642000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>26205000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>25907000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>26838000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>27635000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>27539000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>26701000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>32422000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>32529000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>33668000</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>34336000</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>38248000</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>39463000</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>39837000</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>40088000</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>43744000</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8487,257 +8675,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42916</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42825</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-1335000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-4240000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>2963000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>5785000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>4427000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>5079000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>3743000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>3157000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>5455000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>4762000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-1226000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>4745000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-5975000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>2821000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>3017000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>3248000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>3944000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>4310000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>3758000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>4567000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>1545000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>3172000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-2094000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>2941000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>3002000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>3219000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>2356000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>1901000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>2670000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>2915000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>1827000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>1950000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>1707000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>736000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>-1046000</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>-56000</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>1946000</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>1551000</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>-595000</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>2184000</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8780,130 +8977,134 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>463000</v>
+      </c>
+      <c r="E83" s="3">
         <v>461000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>439000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>513000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>452000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>446000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>441000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>416000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>404000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>427000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>407000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>478000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>427000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>392000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>892000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>959000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>938000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>1120000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>835000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>759000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>690000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>930000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>1328000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>1257000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>2036000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>821000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>936000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>845000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>973000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>898000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>998000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>1158000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>1226000</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>1137000</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>1128000</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>1154000</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>1162000</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>1193000</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>1155000</v>
       </c>
-      <c r="AP83" s="3">
+      <c r="AQ83" s="3">
         <v>1175000</v>
       </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9024,8 +9225,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9146,8 +9350,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9268,8 +9475,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9390,8 +9600,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9512,130 +9725,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>5370000</v>
+      </c>
+      <c r="E89" s="3">
         <v>3918000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>2857000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>7822000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>3293000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>2500000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>3450000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>9291000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>5637000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>3090000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>246000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>7717000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>3704000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1339000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>4430000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>5602000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>4302000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>4761000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>5031000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>4797000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>2490000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>1791000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>4006000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>2173000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>3367000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>707000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>4794000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>4226000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>3084000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>1336000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>3592000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>2793000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>3382000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>1155000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>4015000</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>-1171000</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>3317000</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>286000</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>3632000</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>2971000</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9678,130 +9897,134 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-893000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-991000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1033000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-987000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-764000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1328000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-937000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-783000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-791000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-861000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-989000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-902000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-965000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-1007000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-1149000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-1126000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-1129000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-984000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-1208000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-1172000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-934000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-1134000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-1431000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-1445000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-567000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-986000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-1137000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-959000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-782000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-595000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-929000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-653000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-583000</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-450000</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-715000</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-441000</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-393000</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-339000</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-551000</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AQ91" s="3">
         <v>-409000</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9922,8 +10145,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10044,130 +10270,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-5602000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-10210000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-11201000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-283000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-770000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1487000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1444000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-3845000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1069000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1376000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>53000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-334000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-11443000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-2359000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-1748000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-962000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-1077000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-1173000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-12049000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-1061000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-2707000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-738000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-4778000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-2155000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-882000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-1628000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-763000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>191000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-2425000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>368000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>2178000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>1660000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>673000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-197000</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-58000</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>671000</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-1127000</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>3193000</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-2563000</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>-890000</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10210,130 +10442,134 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>2144000</v>
+      </c>
+      <c r="E96" s="3">
         <v>2105000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>2018000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>2031000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>2077000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>2050000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>1951000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>1953000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>1986000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>1950000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>1852000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>1855000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>1885000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>1853000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-1750000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-1747000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-1770000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-1745000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-1643000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-1649000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-1673000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-1645000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-1542000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-1545000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-1577000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-1551000</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-1405000</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-1394000</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-1468000</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-1428000</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-1277000</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-1285000</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-1311000</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-1299000</v>
-      </c>
-      <c r="AK96" s="3">
-        <v>-1283000</v>
       </c>
       <c r="AL96" s="3">
         <v>-1283000</v>
       </c>
       <c r="AM96" s="3">
+        <v>-1283000</v>
+      </c>
+      <c r="AN96" s="3">
         <v>-1307000</v>
       </c>
-      <c r="AN96" s="3">
+      <c r="AO96" s="3">
         <v>-1294000</v>
       </c>
-      <c r="AO96" s="3">
+      <c r="AP96" s="3">
         <v>-1271000</v>
       </c>
-      <c r="AP96" s="3">
+      <c r="AQ96" s="3">
         <v>-1274000</v>
       </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10454,8 +10690,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10576,8 +10815,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10698,370 +10940,382 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>1762000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-2981000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>4751000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>2638000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-3556000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-5755000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-3009000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-2425000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>1216000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-2814000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-2245000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-4269000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>3758000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-2054000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-1554000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-2702000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-1777000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-3086000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>5207000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-2274000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>1758000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-2098000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>1372000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-3851000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>1137000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-1490000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-2011000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-3152000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-2084000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-1614000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-5566000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-1905000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-2967000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-2722000</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-5785000</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>536000</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-6218000</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>1461000</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>-1977000</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>-835000</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>374000</v>
+      </c>
+      <c r="E101" s="3">
         <v>156000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-367000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>294000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-82000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-138000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>186000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-157000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-93000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>87000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>366000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-412000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-309000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-55000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>366000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-412000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-309000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-55000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-68000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-46000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>78000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-97000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>164000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>87000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>65000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-63000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>43000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-54000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>8000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>20000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-65000</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-32000</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-262000</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>154000</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>19000</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>79000</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>106000</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>253000</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AP101" s="3">
         <v>-484000</v>
       </c>
-      <c r="AP101" s="3">
+      <c r="AQ101" s="3">
         <v>53000</v>
       </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>1493000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-9292000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-3570000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>10187000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-659000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-4586000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-1370000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>3315000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>5702000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-1238000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-1760000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>2957000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-4074000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-2987000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>1494000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>1526000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>1139000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>447000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-1879000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>1416000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>1619000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-1142000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>764000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-3746000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>3687000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-2474000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>2063000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>1211000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-1417000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>110000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>139000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>2516000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>826000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-1610000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-1809000</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>115000</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>-3922000</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>5193000</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>-1392000</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>1299000</v>
       </c>
     </row>
